--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484705_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484705_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.889699999999999</v>
+        <v>8.708</v>
       </c>
       <c r="E2" t="n">
-        <v>8.493399999999999</v>
+        <v>8.6586</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3962</v>
+        <v>0.0494</v>
       </c>
       <c r="G2" t="n">
         <v>2.8261</v>
@@ -610,13 +610,13 @@
         <v>2.7489</v>
       </c>
       <c r="S2" t="n">
-        <v>1.1081</v>
+        <v>0.9265</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0565</v>
+        <v>0.1086</v>
       </c>
       <c r="U2" t="n">
-        <v>1.1647</v>
+        <v>0.8178</v>
       </c>
       <c r="V2" t="n">
         <v>3.4894</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. NEBOT GARCIA</t>
+          <t>A. ALBA GONZALEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.424</v>
+        <v>1.7041</v>
       </c>
       <c r="E3" t="n">
-        <v>1.2091</v>
+        <v>1.677</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2149</v>
+        <v>0.0271</v>
       </c>
       <c r="G3" t="n">
-        <v>2.6248</v>
+        <v>-2.1449</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7784</v>
+        <v>0.4294</v>
       </c>
       <c r="I3" t="n">
-        <v>1.8464</v>
+        <v>-2.5743</v>
       </c>
       <c r="J3" t="n">
-        <v>1.7855</v>
+        <v>0.5284</v>
       </c>
       <c r="K3" t="n">
-        <v>1.0929</v>
+        <v>1.0187</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6925</v>
+        <v>-0.4902</v>
       </c>
       <c r="M3" t="n">
-        <v>0.8394</v>
+        <v>-2.6733</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.3145</v>
+        <v>-0.5893</v>
       </c>
       <c r="O3" t="n">
-        <v>1.1538</v>
+        <v>-2.084</v>
       </c>
       <c r="P3" t="n">
-        <v>0.5498</v>
+        <v>1.0995</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-1.0995</v>
       </c>
       <c r="R3" t="n">
-        <v>0.5498</v>
+        <v>2.1991</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1825</v>
+        <v>0.2155</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2753</v>
+        <v>-0.2858</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0927</v>
+        <v>0.5013</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.5681</v>
+        <v>2.5339</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.3011</v>
+        <v>2.5339</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.267</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. ARIJA DE LA PEÑA</t>
+          <t>M. NEBOT GARCIA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2753</v>
+        <v>1.6714</v>
       </c>
       <c r="E4" t="n">
-        <v>1.2753</v>
+        <v>1.4564</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>0.2149</v>
       </c>
       <c r="G4" t="n">
-        <v>1.2753</v>
+        <v>2.6248</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6502</v>
+        <v>0.7784</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6251</v>
+        <v>1.8464</v>
       </c>
       <c r="J4" t="n">
-        <v>1.2753</v>
+        <v>1.7855</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6502</v>
+        <v>1.0929</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6251</v>
+        <v>0.6925</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>0.8394</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>-0.3145</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.1538</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>0.5498</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>0.5498</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>0.0648</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>-0.0279</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>0.0927</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-1.5681</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>-0.3011</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. ALBA GONZALEZ</t>
+          <t>D. ARIJA DE LA PEÑA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8381999999999999</v>
+        <v>1.2753</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9350000000000001</v>
+        <v>1.2753</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0968</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.1449</v>
+        <v>1.2753</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4294</v>
+        <v>0.6502</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.5743</v>
+        <v>0.6251</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5284</v>
+        <v>1.2753</v>
       </c>
       <c r="K5" t="n">
-        <v>1.0187</v>
+        <v>0.6502</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.4902</v>
+        <v>0.6251</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.6733</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5893</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.084</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.0995</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.0995</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.1991</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.6505</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.0279</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3774</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>2.5339</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>2.5339</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. ARIJA DE LA PENA</t>
+          <t>M. PERAL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4328</v>
+        <v>0.7262</v>
       </c>
       <c r="E6" t="n">
-        <v>1.7575</v>
+        <v>1.1388</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.3247</v>
+        <v>-0.4126</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.3793</v>
+        <v>0.2284</v>
       </c>
       <c r="H6" t="n">
-        <v>2.1402</v>
+        <v>2.6678</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.5196</v>
+        <v>-2.4394</v>
       </c>
       <c r="J6" t="n">
-        <v>3.161</v>
+        <v>3.1519</v>
       </c>
       <c r="K6" t="n">
-        <v>3.7247</v>
+        <v>4.3408</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.5637</v>
+        <v>-1.1889</v>
       </c>
       <c r="M6" t="n">
-        <v>-3.5403</v>
+        <v>-2.9235</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.5845</v>
+        <v>-1.673</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.9558</v>
+        <v>-1.2505</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.733</v>
+        <v>0.1833</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.1154</v>
+        <v>-2.0158</v>
       </c>
       <c r="R6" t="n">
-        <v>2.3823</v>
+        <v>2.1991</v>
       </c>
       <c r="S6" t="n">
-        <v>2.1787</v>
+        <v>0.6365</v>
       </c>
       <c r="T6" t="n">
-        <v>1.0785</v>
+        <v>0.0027</v>
       </c>
       <c r="U6" t="n">
-        <v>1.1002</v>
+        <v>0.6338</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.6335</v>
+        <v>-0.3219</v>
       </c>
       <c r="W6" t="n">
-        <v>0.6335</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.267</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2673</v>
+        <v>0.6054</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0132</v>
+        <v>0.3017</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2541</v>
+        <v>0.3037</v>
       </c>
       <c r="G7" t="n">
         <v>-0.3839</v>
@@ -1000,13 +1000,13 @@
         <v>0.9163</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4428</v>
+        <v>-0.1048</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4404</v>
+        <v>-0.152</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0024</v>
+        <v>0.0471</v>
       </c>
       <c r="V7" t="n">
         <v>1.2774</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1557</v>
+        <v>0.2053</v>
       </c>
       <c r="E8" t="n">
         <v>0.5835</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.4278</v>
+        <v>-0.3782</v>
       </c>
       <c r="G8" t="n">
         <v>-0.1337</v>
@@ -1078,13 +1078,13 @@
         <v>0.3665</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0771</v>
+        <v>-0.0275</v>
       </c>
       <c r="T8" t="n">
         <v>-0.1101</v>
       </c>
       <c r="U8" t="n">
-        <v>0.033</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.08210000000000001</v>
+        <v>0.1069</v>
       </c>
       <c r="E9" t="n">
         <v>0.5709</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4888</v>
+        <v>-0.464</v>
       </c>
       <c r="G9" t="n">
         <v>-1.1463</v>
@@ -1156,13 +1156,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0385</v>
+        <v>-0.0138</v>
       </c>
       <c r="T9" t="n">
         <v>-0.0551</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0165</v>
+        <v>0.0413</v>
       </c>
       <c r="V9" t="n">
         <v>1.267</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0368</v>
+        <v>0.0529</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.4413</v>
+        <v>-1.0288</v>
       </c>
       <c r="F10" t="n">
-        <v>1.4781</v>
+        <v>1.0817</v>
       </c>
       <c r="G10" t="n">
         <v>1.0563</v>
@@ -1234,13 +1234,13 @@
         <v>3.1154</v>
       </c>
       <c r="S10" t="n">
-        <v>1.0751</v>
+        <v>1.0912</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2586</v>
+        <v>0.1539</v>
       </c>
       <c r="U10" t="n">
-        <v>1.3337</v>
+        <v>0.9374</v>
       </c>
       <c r="V10" t="n">
         <v>0.6543</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. PERAL</t>
+          <t>D. ARIJA DE LA PENA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.1352</v>
+        <v>-0.243</v>
       </c>
       <c r="E11" t="n">
-        <v>0.8224</v>
+        <v>1.3047</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.9576</v>
+        <v>-1.5477</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2284</v>
+        <v>-0.3793</v>
       </c>
       <c r="H11" t="n">
-        <v>2.6678</v>
+        <v>2.1402</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.4394</v>
+        <v>-2.5196</v>
       </c>
       <c r="J11" t="n">
-        <v>3.1519</v>
+        <v>3.161</v>
       </c>
       <c r="K11" t="n">
-        <v>4.3408</v>
+        <v>3.7247</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.1889</v>
+        <v>-0.5637</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.9235</v>
+        <v>-3.5403</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.673</v>
+        <v>-1.5845</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.2505</v>
+        <v>-1.9558</v>
       </c>
       <c r="P11" t="n">
-        <v>0.1833</v>
+        <v>-0.733</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.0158</v>
+        <v>-3.1154</v>
       </c>
       <c r="R11" t="n">
-        <v>2.1991</v>
+        <v>2.3823</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2249</v>
+        <v>1.5028</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3137</v>
+        <v>0.6256</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0888</v>
+        <v>0.8772</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.3219</v>
+        <v>-0.6335</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.6335</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.3219</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.6113</v>
+        <v>-2.0807</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.7104</v>
+        <v>-1.3284</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.9009</v>
+        <v>-0.7523</v>
       </c>
       <c r="G12" t="n">
         <v>-0.8589</v>
@@ -1390,13 +1390,13 @@
         <v>1.0995</v>
       </c>
       <c r="S12" t="n">
-        <v>0.7582</v>
+        <v>0.2888</v>
       </c>
       <c r="T12" t="n">
-        <v>0.7677</v>
+        <v>0.1497</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0095</v>
+        <v>0.1391</v>
       </c>
       <c r="V12" t="n">
         <v>0.3219</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.5054</v>
+        <v>-2.4806</v>
       </c>
       <c r="E13" t="n">
         <v>-0.9497</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.5557</v>
+        <v>-1.531</v>
       </c>
       <c r="G13" t="n">
         <v>-0.0272</v>
@@ -1468,13 +1468,13 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2949</v>
+        <v>-0.2702</v>
       </c>
       <c r="T13" t="n">
         <v>-0.0551</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2399</v>
+        <v>-0.2151</v>
       </c>
       <c r="V13" t="n">
         <v>-1.267</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>9.149999999999999</v>
+        <v>10.2512</v>
       </c>
       <c r="E14" t="n">
-        <v>12.5589</v>
+        <v>13.66</v>
       </c>
       <c r="F14" t="n">
         <v>-3.409</v>
@@ -1525,7 +1525,7 @@
         <v>21.7663</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.6003</v>
+        <v>-1.600299999999999</v>
       </c>
       <c r="M14" t="n">
         <v>-17.2293</v>
@@ -1546,16 +1546,16 @@
         <v>15.5769</v>
       </c>
       <c r="S14" t="n">
-        <v>3.2089</v>
+        <v>4.3098</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.7465000000000003</v>
+        <v>0.3545</v>
       </c>
       <c r="U14" t="n">
         <v>3.9552</v>
       </c>
       <c r="V14" t="n">
-        <v>5.753399999999999</v>
+        <v>5.753400000000001</v>
       </c>
       <c r="W14" t="n">
         <v>11.4652</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.3142</v>
+        <v>5.082</v>
       </c>
       <c r="E15" t="n">
-        <v>5.0995</v>
+        <v>5.3879</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.7853</v>
+        <v>-0.306</v>
       </c>
       <c r="G15" t="n">
         <v>2.7628</v>
@@ -1624,13 +1624,13 @@
         <v>2.3823</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.4645</v>
+        <v>-0.6966</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.101</v>
+        <v>-0.8126</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3634</v>
+        <v>0.1159</v>
       </c>
       <c r="V15" t="n">
         <v>0.6335</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.3518</v>
+        <v>3.0414</v>
       </c>
       <c r="E16" t="n">
-        <v>3.3727</v>
+        <v>3.2766</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0209</v>
+        <v>-0.2352</v>
       </c>
       <c r="G16" t="n">
         <v>2.8352</v>
@@ -1702,13 +1702,13 @@
         <v>2.7489</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4207</v>
+        <v>0.1103</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.46</v>
+        <v>-0.5562</v>
       </c>
       <c r="U16" t="n">
-        <v>0.8807</v>
+        <v>0.6665</v>
       </c>
       <c r="V16" t="n">
         <v>-0.8204</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.7324</v>
+        <v>1.3871</v>
       </c>
       <c r="E17" t="n">
-        <v>1.9641</v>
+        <v>1.3872</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2317</v>
+        <v>-0.0001</v>
       </c>
       <c r="G17" t="n">
         <v>0.7789</v>
@@ -1780,13 +1780,13 @@
         <v>2.9321</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2949</v>
+        <v>-0.0503</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0709</v>
+        <v>-0.506</v>
       </c>
       <c r="U17" t="n">
-        <v>0.224</v>
+        <v>0.4557</v>
       </c>
       <c r="V17" t="n">
         <v>1.3916</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2354</v>
+        <v>0.394</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.5605</v>
+        <v>-0.07969999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3251</v>
+        <v>0.4737</v>
       </c>
       <c r="G18" t="n">
         <v>-0.4953</v>
@@ -1858,13 +1858,13 @@
         <v>1.0995</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.781</v>
+        <v>-0.1516</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6056</v>
+        <v>-0.1248</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1754</v>
+        <v>-0.0268</v>
       </c>
       <c r="V18" t="n">
         <v>0.1246</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. SOLBES SORIANO</t>
+          <t>F. BLASCO MANZANO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.3085</v>
+        <v>-1.122</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.0057</v>
+        <v>0.7423</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.3027</v>
+        <v>-1.8643</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.2884</v>
+        <v>-0.3081</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.5062</v>
+        <v>-1.7409</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.7823</v>
+        <v>1.4328</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.4092</v>
+        <v>3.4975</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1484</v>
+        <v>1.263</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.5577</v>
+        <v>2.2345</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.8792</v>
+        <v>-3.8056</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.6546</v>
+        <v>-3.0039</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.2246</v>
+        <v>-0.8017</v>
       </c>
       <c r="P19" t="n">
-        <v>0.1833</v>
+        <v>0.5498</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.0995</v>
+        <v>-1.8326</v>
       </c>
       <c r="R19" t="n">
-        <v>1.2828</v>
+        <v>2.3823</v>
       </c>
       <c r="S19" t="n">
-        <v>0.4956</v>
+        <v>-0.7198</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2361</v>
+        <v>-0.9227</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2595</v>
+        <v>0.2029</v>
       </c>
       <c r="V19" t="n">
-        <v>0.3011</v>
+        <v>-0.6439</v>
       </c>
       <c r="W19" t="n">
-        <v>1.267</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.9658</v>
+        <v>-0.6439</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. CARRION BALLESTER</t>
+          <t>R. MEDINA LERMA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.4176</v>
+        <v>-1.1285</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.3488</v>
+        <v>-1.2876</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.0688</v>
+        <v>0.1591</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.1281</v>
+        <v>-0.9488</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.0095</v>
+        <v>-1.7339</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1187</v>
+        <v>0.7851</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.5343</v>
+        <v>0.0008</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.576</v>
+        <v>-0.2075</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0417</v>
+        <v>0.2084</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.5938</v>
+        <v>-0.9496</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.4335</v>
+        <v>-1.5264</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1603</v>
+        <v>0.5768</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.3665</v>
+        <v>0.1833</v>
       </c>
       <c r="Q20" t="n">
         <v>-0.9163</v>
       </c>
       <c r="R20" t="n">
-        <v>0.5498</v>
+        <v>1.0995</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0771</v>
+        <v>-0.3526</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1652</v>
+        <v>-0.3722</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2422</v>
+        <v>0.0196</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.0104</v>
       </c>
       <c r="W20" t="n">
-        <v>1.267</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.267</v>
+        <v>-0.0104</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.4881</v>
+        <v>-1.4633</v>
       </c>
       <c r="E21" t="n">
         <v>-0.6544</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8337</v>
+        <v>-0.8089</v>
       </c>
       <c r="G21" t="n">
         <v>-1.4496</v>
@@ -2092,13 +2092,13 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0385</v>
+        <v>-0.0138</v>
       </c>
       <c r="T21" t="n">
         <v>-0.0551</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0165</v>
+        <v>0.0413</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>R. MEDINA LERMA</t>
+          <t>A. CARRION BALLESTER</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.5452</v>
+        <v>-1.4671</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.5761</v>
+        <v>-0.3488</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0309</v>
+        <v>-1.1183</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.9488</v>
+        <v>-1.1281</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.7339</v>
+        <v>-1.0095</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7851</v>
+        <v>-0.1187</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0008</v>
+        <v>-0.5343</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.2075</v>
+        <v>-0.576</v>
       </c>
       <c r="L22" t="n">
-        <v>0.2084</v>
+        <v>0.0417</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.9496</v>
+        <v>-0.5938</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.5264</v>
+        <v>-0.4335</v>
       </c>
       <c r="O22" t="n">
-        <v>0.5768</v>
+        <v>-0.1603</v>
       </c>
       <c r="P22" t="n">
-        <v>0.1833</v>
+        <v>-0.3665</v>
       </c>
       <c r="Q22" t="n">
         <v>-0.9163</v>
       </c>
       <c r="R22" t="n">
-        <v>1.0995</v>
+        <v>0.5498</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7692</v>
+        <v>0.0275</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6606</v>
+        <v>-0.1652</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1086</v>
+        <v>0.1927</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.0104</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.267</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.0104</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>F. BLASCO MANZANO</t>
+          <t>A. SOLBES SORIANO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.8651</v>
+        <v>-1.9102</v>
       </c>
       <c r="E23" t="n">
-        <v>0.4538</v>
+        <v>-0.5827</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.3189</v>
+        <v>-1.3275</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.3081</v>
+        <v>-2.2884</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.7409</v>
+        <v>-1.5062</v>
       </c>
       <c r="I23" t="n">
-        <v>1.4328</v>
+        <v>-0.7823</v>
       </c>
       <c r="J23" t="n">
-        <v>3.4975</v>
+        <v>-0.4092</v>
       </c>
       <c r="K23" t="n">
-        <v>1.263</v>
+        <v>0.1484</v>
       </c>
       <c r="L23" t="n">
-        <v>2.2345</v>
+        <v>-0.5577</v>
       </c>
       <c r="M23" t="n">
-        <v>-3.8056</v>
+        <v>-1.8792</v>
       </c>
       <c r="N23" t="n">
-        <v>-3.0039</v>
+        <v>-1.6546</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.8017</v>
+        <v>-0.2246</v>
       </c>
       <c r="P23" t="n">
-        <v>0.5498</v>
+        <v>0.1833</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.8326</v>
+        <v>-1.0995</v>
       </c>
       <c r="R23" t="n">
-        <v>2.3823</v>
+        <v>1.2828</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.4629</v>
+        <v>-0.1061</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.2111</v>
+        <v>-0.3409</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2517</v>
+        <v>0.2347</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.6439</v>
+        <v>0.3011</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.267</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.6439</v>
+        <v>-0.9658</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.8426</v>
+        <v>-3.0465</v>
       </c>
       <c r="E24" t="n">
-        <v>0.3337</v>
+        <v>-0.1471</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.1762</v>
+        <v>-2.8994</v>
       </c>
       <c r="G24" t="n">
         <v>-0.319</v>
@@ -2326,13 +2326,13 @@
         <v>1.8326</v>
       </c>
       <c r="S24" t="n">
-        <v>0.391</v>
+        <v>0.187</v>
       </c>
       <c r="T24" t="n">
-        <v>0.6214</v>
+        <v>0.1407</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2305</v>
+        <v>0.0464</v>
       </c>
       <c r="V24" t="n">
         <v>-2.7313</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.8802</v>
+        <v>-3.1993</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.619</v>
+        <v>-2.7151</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.2612</v>
+        <v>-0.4841</v>
       </c>
       <c r="G25" t="n">
         <v>-2.9698</v>
@@ -2404,13 +2404,13 @@
         <v>0.9163</v>
       </c>
       <c r="S25" t="n">
-        <v>0.2729</v>
+        <v>-0.0462</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.0746</v>
+        <v>-0.1708</v>
       </c>
       <c r="U25" t="n">
-        <v>0.3476</v>
+        <v>0.1246</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-4.9659</v>
+        <v>-4.4356</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.0505</v>
+        <v>-1.5697</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.9155</v>
+        <v>-2.8659</v>
       </c>
       <c r="G26" t="n">
         <v>0.5936</v>
@@ -2482,13 +2482,13 @@
         <v>1.0995</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.6449</v>
+        <v>-0.1146</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.5505</v>
+        <v>-0.0697</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.0944</v>
+        <v>-0.0449</v>
       </c>
       <c r="V26" t="n">
         <v>-3.9982</v>
@@ -2515,16 +2515,16 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-9.150199999999998</v>
+        <v>-7.867999999999999</v>
       </c>
       <c r="E27" t="n">
-        <v>3.408800000000002</v>
+        <v>3.4089</v>
       </c>
       <c r="F27" t="n">
-        <v>-12.5589</v>
+        <v>-11.2769</v>
       </c>
       <c r="G27" t="n">
-        <v>-2.9366</v>
+        <v>-2.936600000000001</v>
       </c>
       <c r="H27" t="n">
         <v>-13.3553</v>
@@ -2551,7 +2551,7 @@
         <v>1.6004</v>
       </c>
       <c r="P27" t="n">
-        <v>2.7489</v>
+        <v>2.748899999999999</v>
       </c>
       <c r="Q27" t="n">
         <v>-15.5768</v>
@@ -2560,16 +2560,16 @@
         <v>18.3256</v>
       </c>
       <c r="S27" t="n">
-        <v>-3.2088</v>
+        <v>-1.9268</v>
       </c>
       <c r="T27" t="n">
-        <v>-3.9553</v>
+        <v>-3.9555</v>
       </c>
       <c r="U27" t="n">
-        <v>0.7464999999999999</v>
+        <v>2.0286</v>
       </c>
       <c r="V27" t="n">
-        <v>-5.753400000000001</v>
+        <v>-5.7534</v>
       </c>
       <c r="W27" t="n">
         <v>5.7118</v>
